--- a/data/trans_orig/P44-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71826</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82605</t>
+          <t>82482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>84021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98074</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160178</t>
+          <t>160498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177904</t>
+          <t>177422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>36423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>60378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135736</t>
+          <t>136563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157649</t>
+          <t>157723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182504</t>
+          <t>182066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201640</t>
+          <t>200695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>326018</t>
+          <t>326149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353648</t>
+          <t>354674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95197</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107743</t>
+          <t>108696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127566</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141819</t>
+          <t>141721</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228433</t>
+          <t>227650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246802</t>
+          <t>247494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37121</t>
+          <t>37089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117574</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133187</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136267</t>
+          <t>136380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151403</t>
+          <t>151455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260856</t>
+          <t>260888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281809</t>
+          <t>281467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64627</t>
+          <t>65152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>75038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76248</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86368</t>
+          <t>87257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145317</t>
+          <t>145991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160282</t>
+          <t>159551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90358</t>
+          <t>89860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102575</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>117299</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126835</t>
+          <t>127727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212001</t>
+          <t>211549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227939</t>
+          <t>227484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28705</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209570</t>
+          <t>210041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227959</t>
+          <t>228006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259944</t>
+          <t>261738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>281335</t>
+          <t>282034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477872</t>
+          <t>477556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505720</t>
+          <t>505338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57987</t>
+          <t>58799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>219532</t>
+          <t>218708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>241967</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>302994</t>
+          <t>301831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>319100</t>
+          <t>318135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>529809</t>
+          <t>528997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>556726</t>
+          <t>555664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138282</t>
+          <t>138120</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>89516</t>
+          <t>91432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131398</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>194216</t>
+          <t>196684</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>254540</t>
+          <t>256243</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1055767</t>
+          <t>1055929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1101285</t>
+          <t>1102108</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1336082</t>
+          <t>1333678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1377964</t>
+          <t>1376048</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2406988</t>
+          <t>2405285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2467312</t>
+          <t>2464844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70235</t>
+          <t>72328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88525</t>
+          <t>89546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82166</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97993</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159733</t>
+          <t>159479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182343</t>
+          <t>182945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>27804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188867</t>
+          <t>190033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203563</t>
+          <t>204002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228153</t>
+          <t>228146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239039</t>
+          <t>239821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422046</t>
+          <t>423819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440734</t>
+          <t>440970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>30335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>55093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111096</t>
+          <t>111037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128335</t>
+          <t>128338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128873</t>
+          <t>128619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147823</t>
+          <t>146991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244452</t>
+          <t>246571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271777</t>
+          <t>271132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>31292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62102</t>
+          <t>62168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126576</t>
+          <t>126118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144967</t>
+          <t>145261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154556</t>
+          <t>154743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173413</t>
+          <t>173228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287754</t>
+          <t>287688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314655</t>
+          <t>315509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79140</t>
+          <t>78500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>86116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97420</t>
+          <t>96491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105499</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179961</t>
+          <t>180069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190779</t>
+          <t>190657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96386</t>
+          <t>96027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109124</t>
+          <t>109131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118452</t>
+          <t>119544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131064</t>
+          <t>131665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219894</t>
+          <t>220520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237889</t>
+          <t>237756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>55958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>87621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208082</t>
+          <t>208045</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231277</t>
+          <t>231683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247060</t>
+          <t>246078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268776</t>
+          <t>269142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>459281</t>
+          <t>463211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>494082</t>
+          <t>494874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27926</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53331</t>
+          <t>54201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276361</t>
+          <t>275203</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297245</t>
+          <t>297323</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>346859</t>
+          <t>346905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>362496</t>
+          <t>362670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>631590</t>
+          <t>630720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>656995</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141704</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191956</t>
+          <t>191432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98308</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141896</t>
+          <t>145022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>250835</t>
+          <t>254479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>316911</t>
+          <t>319383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1207570</t>
+          <t>1208094</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1257822</t>
+          <t>1258023</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1453910</t>
+          <t>1450784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1497498</t>
+          <t>1495875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2678421</t>
+          <t>2675949</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2744497</t>
+          <t>2740853</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023 (tasa de respuesta: 98,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63576</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>82569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>96615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>121293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86944</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101021</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138410</t>
+          <t>138215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163938</t>
+          <t>162893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77518</t>
+          <t>77862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50300</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86677</t>
+          <t>87980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120968</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120562</t>
+          <t>120218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146730</t>
+          <t>147823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184250</t>
+          <t>185738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202813</t>
+          <t>203609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311662</t>
+          <t>312392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>345953</t>
+          <t>344650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47480</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>67608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47017</t>
+          <t>47649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64487</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99685</t>
+          <t>99431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126561</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90527</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110175</t>
+          <t>110499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101000</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118470</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196581</t>
+          <t>196794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223457</t>
+          <t>223711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63972</t>
+          <t>65100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>50463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97615</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125930</t>
+          <t>126537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105154</t>
+          <t>104026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126373</t>
+          <t>127051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122637</t>
+          <t>122129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140825</t>
+          <t>140759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234418</t>
+          <t>233811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262733</t>
+          <t>262258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58163</t>
+          <t>58550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67574</t>
+          <t>68382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>84879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93072</t>
+          <t>92975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146588</t>
+          <t>146518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158954</t>
+          <t>158388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>37475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59858</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80722</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>84626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101765</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91328</t>
+          <t>91048</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104014</t>
+          <t>104366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180705</t>
+          <t>181063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201569</t>
+          <t>202586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91225</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124201</t>
+          <t>124833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201122</t>
+          <t>199055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>98562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>308181</t>
+          <t>310351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>167865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201473</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>303459</t>
+          <t>305526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>466978</t>
+          <t>466113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>489098</t>
+          <t>486928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>699586</t>
+          <t>698717</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>224581</t>
+          <t>224856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>499781</t>
+          <t>492777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116400</t>
+          <t>114763</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144381</t>
+          <t>143551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347985</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>706041</t>
+          <t>689124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53702</t>
+          <t>60706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328902</t>
+          <t>328627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206008</t>
+          <t>206838</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>233989</t>
+          <t>235626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>214748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>555887</t>
+          <t>559196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>613221</t>
+          <t>611744</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1137669</t>
+          <t>1112299</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>315898</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>550702</t>
+          <t>548100</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1034627</t>
+          <t>1025251</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1733043</t>
+          <t>1748115</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>572355</t>
+          <t>597725</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1096803</t>
+          <t>1098280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1257260</t>
+          <t>1259862</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1492064</t>
+          <t>1504616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1784943</t>
+          <t>1769871</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2483359</t>
+          <t>2492735</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P44-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>71547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82482</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>83399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160498</t>
+          <t>160849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177422</t>
+          <t>177605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60378</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157723</t>
+          <t>157491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182066</t>
+          <t>182660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200695</t>
+          <t>200760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>326149</t>
+          <t>326476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>354674</t>
+          <t>354594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95905</t>
+          <t>95259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108696</t>
+          <t>108614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126368</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141721</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227650</t>
+          <t>227508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247494</t>
+          <t>247433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118007</t>
+          <t>118655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136380</t>
+          <t>136117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151455</t>
+          <t>151311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260888</t>
+          <t>260257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281467</t>
+          <t>281779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>63202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75038</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>76483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87257</t>
+          <t>86372</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159551</t>
+          <t>160269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89860</t>
+          <t>89781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117299</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127727</t>
+          <t>126848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>211549</t>
+          <t>211554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227484</t>
+          <t>227299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>29812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210041</t>
+          <t>208463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228006</t>
+          <t>227866</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261738</t>
+          <t>261101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282034</t>
+          <t>281722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477556</t>
+          <t>477106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>505338</t>
+          <t>505582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,82 +3148,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>15045</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>8459</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>23753</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>43052</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>30792</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>58883</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>15045</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>8579</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>24883</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>43052</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>32132</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>58799</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>218708</t>
+          <t>219561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>241967</t>
+          <t>242177</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,82 +3261,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>311669</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>302961</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>318255</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>544744</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>528913</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>557004</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>92,68%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>311669</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>301831</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>318135</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>544744</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>528997</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>555664</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>92930</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133802</t>
+          <t>131805</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256243</t>
+          <t>257344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1055929</t>
+          <t>1057096</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1102108</t>
+          <t>1101119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1333678</t>
+          <t>1335675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1376048</t>
+          <t>1377246</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2405285</t>
+          <t>2404184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2464844</t>
+          <t>2466839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53824</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>71412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89546</t>
+          <t>88915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>81233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97435</t>
+          <t>97249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159479</t>
+          <t>160444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182945</t>
+          <t>183933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190033</t>
+          <t>190357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204002</t>
+          <t>203882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228146</t>
+          <t>228860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239821</t>
+          <t>239718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423819</t>
+          <t>423091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440970</t>
+          <t>440846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30335</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55093</t>
+          <t>57236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111037</t>
+          <t>112052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128338</t>
+          <t>128641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128619</t>
+          <t>126476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146991</t>
+          <t>146894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246571</t>
+          <t>244428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271132</t>
+          <t>270355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62168</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126118</t>
+          <t>125773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145261</t>
+          <t>145254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154743</t>
+          <t>153717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173228</t>
+          <t>174133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287688</t>
+          <t>287104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315509</t>
+          <t>313558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78500</t>
+          <t>79999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>97285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105508</t>
+          <t>105551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180069</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190657</t>
+          <t>190726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96027</t>
+          <t>94786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>108811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119544</t>
+          <t>118531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131665</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>220520</t>
+          <t>220972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237756</t>
+          <t>237973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>30567</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53884</t>
+          <t>55762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42825</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55958</t>
+          <t>54458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87621</t>
+          <t>88690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208045</t>
+          <t>206167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231683</t>
+          <t>231362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246078</t>
+          <t>248493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269142</t>
+          <t>270053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>463211</t>
+          <t>462142</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>494874</t>
+          <t>496374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27785</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54201</t>
+          <t>53283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275203</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297323</t>
+          <t>297962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>346905</t>
+          <t>347071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>362670</t>
+          <t>362690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>630720</t>
+          <t>631638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>657115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141503</t>
+          <t>140424</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191432</t>
+          <t>189496</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99931</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145022</t>
+          <t>143470</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>253370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>319383</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1208094</t>
+          <t>1210030</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1258023</t>
+          <t>1259102</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1450784</t>
+          <t>1452336</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1495875</t>
+          <t>1497576</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2675949</t>
+          <t>2673292</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2740853</t>
+          <t>2741962</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>62602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82569</t>
+          <t>83794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96615</t>
+          <t>97765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121293</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56198</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46996</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>75854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>97993</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>90474</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100637</t>
+          <t>104109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>150462</t>
+          <t>162910</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138215</t>
+          <t>149632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162893</t>
+          <t>175354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>64,2%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>134663</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>134663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>134663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>273119</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>273119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>273119</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77862</t>
+          <t>80305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>33508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>108247</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87980</t>
+          <t>92373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120238</t>
+          <t>126954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>134529</t>
+          <t>142802</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120218</t>
+          <t>128567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147823</t>
+          <t>155430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>195033</t>
+          <t>205383</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185738</t>
+          <t>195719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203609</t>
+          <t>214051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>329561</t>
+          <t>348184</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312392</t>
+          <t>329477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344650</t>
+          <t>364058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>208872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>208872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>208872</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>234550</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>234550</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234550</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>432630</t>
+          <t>456431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>432630</t>
+          <t>456431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>432630</t>
+          <t>456431</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67608</t>
+          <t>65958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47649</t>
+          <t>47949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>66555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99431</t>
+          <t>100491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126348</t>
+          <t>128244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100855</t>
+          <t>99188</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>88872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110499</t>
+          <t>108106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109733</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100422</t>
+          <t>100192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>118798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>210587</t>
+          <t>208732</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196794</t>
+          <t>193332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223711</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>157655</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157655</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157655</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165487</t>
+          <t>166747</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165487</t>
+          <t>166747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165487</t>
+          <t>166747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>323142</t>
+          <t>321576</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>323142</t>
+          <t>321576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323142</t>
+          <t>321576</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>47967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65100</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,22 +8437,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50463</t>
+          <t>54814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>74532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>124042</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>108259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126537</t>
+          <t>140088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>116256</t>
+          <t>131695</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104026</t>
+          <t>119373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127051</t>
+          <t>143564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,27 +8550,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>132045</t>
+          <t>143475</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122129</t>
+          <t>133149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140759</t>
+          <t>152867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>248302</t>
+          <t>275170</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233811</t>
+          <t>259124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262258</t>
+          <t>290953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169126</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169126</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169126</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191222</t>
+          <t>207681</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191222</t>
+          <t>207681</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191222</t>
+          <t>207681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>360348</t>
+          <t>399212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>360348</t>
+          <t>399212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360348</t>
+          <t>399212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63640</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58550</t>
+          <t>63185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68382</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89330</t>
+          <t>93541</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84879</t>
+          <t>88319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>97406</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>152970</t>
+          <t>162115</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146518</t>
+          <t>154605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158388</t>
+          <t>168497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>103267</t>
+          <t>108286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103267</t>
+          <t>108286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103267</t>
+          <t>108286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>179780</t>
+          <t>190379</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179780</t>
+          <t>190379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179780</t>
+          <t>190379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>45904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69487</t>
+          <t>68866</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>58953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>80276</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>93969</t>
+          <t>94021</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>85954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102112</t>
+          <t>101610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>97971</t>
+          <t>100691</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>93603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>106979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>191940</t>
+          <t>194712</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>181063</t>
+          <t>183302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202586</t>
+          <t>204625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>132904</t>
+          <t>131858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>132904</t>
+          <t>131858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132904</t>
+          <t>131858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>131720</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>131720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>131720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261427</t>
+          <t>263578</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261427</t>
+          <t>263578</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261427</t>
+          <t>263578</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108149</t>
+          <t>124534</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91772</t>
+          <t>107867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124833</t>
+          <t>141682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>121301</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199055</t>
+          <t>150680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>222848</t>
+          <t>259944</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98562</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310351</t>
+          <t>282461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>184549</t>
+          <t>211858</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>194710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200926</t>
+          <t>228525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>389881</t>
+          <t>223182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305526</t>
+          <t>207911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>466113</t>
+          <t>237290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>574431</t>
+          <t>435039</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>486928</t>
+          <t>412522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>698717</t>
+          <t>457557</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>292698</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>292698</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292698</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>504581</t>
+          <t>358591</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>504581</t>
+          <t>358591</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>504581</t>
+          <t>358591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>797279</t>
+          <t>694983</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>797279</t>
+          <t>694983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>797279</t>
+          <t>694983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>373952</t>
+          <t>144487</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>224856</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>492777</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114763</t>
+          <t>132890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>163009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>504059</t>
+          <t>293051</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>269858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>689124</t>
+          <t>315165</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>179531</t>
+          <t>205456</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>189680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328627</t>
+          <t>223330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>220282</t>
+          <t>247679</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206838</t>
+          <t>233233</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>235626</t>
+          <t>263352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>399813</t>
+          <t>453134</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>431020</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>559196</t>
+          <t>476327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553483</t>
+          <t>349943</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553483</t>
+          <t>349943</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553483</t>
+          <t>349943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>350389</t>
+          <t>396242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>350389</t>
+          <t>396242</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>350389</t>
+          <t>396242</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>903872</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>903872</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>903872</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>611744</t>
+          <t>540928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112299</t>
+          <t>611536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>303346</t>
+          <t>501033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>548100</t>
+          <t>558655</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1025251</t>
+          <t>1057958</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1748115</t>
+          <t>1152250</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>929527</t>
+          <t>1018510</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>597725</t>
+          <t>982438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1098280</t>
+          <t>1053046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1328539</t>
+          <t>1221487</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1259862</t>
+          <t>1192834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1504616</t>
+          <t>1250456</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2258066</t>
+          <t>2239996</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1769871</t>
+          <t>2193213</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2492735</t>
+          <t>2287505</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
